--- a/ASSESSMENT_1.xlsx
+++ b/ASSESSMENT_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiyas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC45\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18832468-D076-4A41-B20C-F8882C5174C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EE1D6E-9CBF-44B6-87DA-07FAD9EEF358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{C7037B08-DA07-4C0A-94A0-CFA73735DD06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C7037B08-DA07-4C0A-94A0-CFA73735DD06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales_Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Student_Marks" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sales_Data!$F$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sales_Data!$E$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>Order_ID</t>
   </si>
@@ -195,14 +195,30 @@
   </si>
   <si>
     <t>Left</t>
+  </si>
+  <si>
+    <t>Total No. of Order</t>
+  </si>
+  <si>
+    <t>Product Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Sales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">East </t>
+  </si>
+  <si>
+    <t xml:space="preserve">West </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -341,19 +357,36 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="4"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="5"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="5" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="5" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -440,9 +473,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -480,7 +513,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -586,7 +619,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -728,7 +761,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -736,468 +769,497 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAACAB9-7624-49DE-9D30-6E31735D10DA}">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>301</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="15" t="str">
+        <f>LEFT(C2,2)</f>
+        <v>Am</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="15">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="G2" s="15" t="str">
+        <f t="shared" ref="G2:G7" si="0">IF(F2&gt;=3,"High","Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="H2" s="16">
+        <v>45000</v>
+      </c>
+      <c r="I2" s="16">
+        <f>ROUND(H2,10000)</f>
+        <v>45000</v>
+      </c>
+      <c r="J2" s="16">
+        <f t="shared" ref="J2:J7" si="1">PRODUCT(F2,H2)</f>
+        <v>90000</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="17" t="str">
+        <f t="shared" ref="L2:L7" si="2">TEXT(K2, "MMMM")</f>
+        <v>January</v>
+      </c>
+      <c r="M2" s="18">
+        <f>VLOOKUP(E2,Product_Master!A1:C4,3,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="N2" s="16">
+        <f t="shared" ref="N2:N7" si="3">SUM(J2*0.18)</f>
+        <v>16200</v>
+      </c>
+      <c r="O2" s="16">
+        <f t="shared" ref="O2:O7" si="4">SUM(J2,N2)</f>
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>306</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="15" t="str">
+        <f t="shared" ref="D3:D7" si="5">LEFT(C3,2)</f>
+        <v>Ri</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="15">
+        <v>2</v>
+      </c>
+      <c r="G3" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>Low</v>
+      </c>
+      <c r="H3" s="16">
+        <v>45000</v>
+      </c>
+      <c r="I3" s="16">
+        <f t="shared" ref="I3:I7" si="6">ROUND(H3,10000)</f>
+        <v>45000</v>
+      </c>
+      <c r="J3" s="16">
+        <f t="shared" si="1"/>
+        <v>90000</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>January</v>
+      </c>
+      <c r="M3" s="18">
+        <f>VLOOKUP(E3,Product_Master!A1:C4,3,0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="N3" s="16">
+        <f t="shared" si="3"/>
+        <v>16200</v>
+      </c>
+      <c r="O3" s="16">
+        <f t="shared" si="4"/>
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>302</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>Ri</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="15">
+        <v>5</v>
+      </c>
+      <c r="G4" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+      <c r="H4" s="16">
+        <v>15000</v>
+      </c>
+      <c r="I4" s="16">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="J4" s="16">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>January</v>
+      </c>
+      <c r="M4" s="18">
+        <f>VLOOKUP(E4,Product_Master!A2:C5,3,0)</f>
+        <v>0.12</v>
+      </c>
+      <c r="N4" s="16">
+        <f t="shared" si="3"/>
+        <v>13500</v>
+      </c>
+      <c r="O4" s="16">
+        <f t="shared" si="4"/>
+        <v>88500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
+        <v>305</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>Am</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="15">
+        <v>4</v>
+      </c>
+      <c r="G5" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+      <c r="H5" s="16">
+        <v>15000</v>
+      </c>
+      <c r="I5" s="16">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="J5" s="16">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>January</v>
+      </c>
+      <c r="M5" s="18">
+        <f>VLOOKUP(E5,Product_Master!A2:C5,3,0)</f>
+        <v>0.12</v>
+      </c>
+      <c r="N5" s="16">
+        <f t="shared" si="3"/>
+        <v>10800</v>
+      </c>
+      <c r="O5" s="16">
+        <f t="shared" si="4"/>
+        <v>70800</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="S5" s="8">
+        <f>MAX(O2:O7)</f>
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
+        <v>303</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>Ku</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="15">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>301</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1">
-        <f t="shared" ref="C2:C7" si="0">SUMIF(B2:B7,"North",P2:P7)</f>
-        <v>177000</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="str">
-        <f>LEFT(D2,2)</f>
-        <v>Am</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G6" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+      <c r="H6" s="16">
+        <v>18000</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="6"/>
+        <v>18000</v>
+      </c>
+      <c r="J6" s="16">
+        <f t="shared" si="1"/>
+        <v>54000</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>January</v>
+      </c>
+      <c r="M6" s="18">
+        <f>VLOOKUP(E6,Product_Master!A3:C6,3,0)</f>
+        <v>0.12</v>
+      </c>
+      <c r="N6" s="16">
+        <f t="shared" si="3"/>
+        <v>9720</v>
+      </c>
+      <c r="O6" s="16">
+        <f t="shared" si="4"/>
+        <v>63720</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" s="9">
+        <f>MIN(O2:O7)</f>
+        <v>53100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>304</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>Ne</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="str">
-        <f t="shared" ref="H2:H7" si="1">IF(G2&gt;=3,"High","Low")</f>
+      <c r="F7" s="15">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15" t="str">
+        <f t="shared" si="0"/>
         <v>Low</v>
       </c>
-      <c r="I2" s="1">
+      <c r="H7" s="16">
         <v>45000</v>
       </c>
-      <c r="J2" s="1">
-        <f>ROUND(I2,10000)</f>
+      <c r="I7" s="16">
+        <f t="shared" si="6"/>
         <v>45000</v>
       </c>
-      <c r="K2" s="1">
-        <f t="shared" ref="K2:K7" si="2">PRODUCT(G2,I2)</f>
-        <v>90000</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="5" t="str">
-        <f t="shared" ref="M2:M7" si="3">TEXT(L2, "MMMM")</f>
+      <c r="J7" s="16">
+        <f t="shared" si="1"/>
+        <v>45000</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="17" t="str">
+        <f t="shared" si="2"/>
         <v>January</v>
       </c>
-      <c r="N2" s="4">
-        <f>VLOOKUP(F2,Product_Master!A1:C4,3,0)</f>
+      <c r="M7" s="18">
+        <f>VLOOKUP(E7,Product_Master!A1:C4,3,0)</f>
         <v>0.18</v>
       </c>
-      <c r="O2" s="1">
-        <f t="shared" ref="O2:O7" si="4">SUM(K2*0.18)</f>
-        <v>16200</v>
-      </c>
-      <c r="P2" s="1">
-        <f t="shared" ref="P2:P7" si="5">SUM(K2,O2)</f>
-        <v>106200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>306</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1">
-        <f t="shared" si="0"/>
-        <v>70800</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="str">
-        <f t="shared" ref="E3:E7" si="6">LEFT(D3,2)</f>
-        <v>Ri</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-      <c r="H3" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Low</v>
-      </c>
-      <c r="I3" s="1">
-        <v>45000</v>
-      </c>
-      <c r="J3" s="1">
-        <f t="shared" ref="J3:J7" si="7">ROUND(I3,10000)</f>
-        <v>45000</v>
-      </c>
-      <c r="K3" s="1">
-        <f t="shared" si="2"/>
-        <v>90000</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="5" t="str">
+      <c r="N7" s="16">
         <f t="shared" si="3"/>
-        <v>January</v>
-      </c>
-      <c r="N3" s="4">
-        <f>VLOOKUP(F3,Product_Master!A1:C4,3,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="O3" s="1">
+        <v>8100</v>
+      </c>
+      <c r="O7" s="16">
         <f t="shared" si="4"/>
-        <v>16200</v>
-      </c>
-      <c r="P3" s="1">
-        <f t="shared" si="5"/>
-        <v>106200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>302</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
-        <f t="shared" si="0"/>
-        <v>70800</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>Ri</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1">
-        <v>5</v>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>High</v>
-      </c>
-      <c r="I4" s="1">
-        <v>15000</v>
-      </c>
-      <c r="J4" s="1">
-        <f t="shared" si="7"/>
-        <v>15000</v>
-      </c>
-      <c r="K4" s="1">
-        <f t="shared" si="2"/>
-        <v>75000</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>January</v>
-      </c>
-      <c r="N4" s="4">
-        <f>VLOOKUP(F4,Product_Master!A2:C5,3,0)</f>
-        <v>0.12</v>
-      </c>
-      <c r="O4" s="1">
-        <f t="shared" si="4"/>
-        <v>13500</v>
-      </c>
-      <c r="P4" s="1">
-        <f t="shared" si="5"/>
-        <v>88500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>305</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1">
-        <f t="shared" si="0"/>
-        <v>70800</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>Am</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1">
-        <v>4</v>
-      </c>
-      <c r="H5" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>High</v>
-      </c>
-      <c r="I5" s="1">
-        <v>15000</v>
-      </c>
-      <c r="J5" s="1">
-        <f t="shared" si="7"/>
-        <v>15000</v>
-      </c>
-      <c r="K5" s="1">
-        <f t="shared" si="2"/>
-        <v>60000</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>January</v>
-      </c>
-      <c r="N5" s="4">
-        <f>VLOOKUP(F5,Product_Master!A2:C5,3,0)</f>
-        <v>0.12</v>
-      </c>
-      <c r="O5" s="1">
-        <f t="shared" si="4"/>
-        <v>10800</v>
-      </c>
-      <c r="P5" s="1">
-        <f t="shared" si="5"/>
-        <v>70800</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="S5" s="9">
-        <f>MAX(P2:P7)</f>
-        <v>106200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>303</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>Ku</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>High</v>
-      </c>
-      <c r="I6" s="1">
-        <v>18000</v>
-      </c>
-      <c r="J6" s="1">
-        <f t="shared" si="7"/>
-        <v>18000</v>
-      </c>
-      <c r="K6" s="1">
-        <f t="shared" si="2"/>
-        <v>54000</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>January</v>
-      </c>
-      <c r="N6" s="4">
-        <f>VLOOKUP(F6,Product_Master!A3:C6,3,0)</f>
-        <v>0.12</v>
-      </c>
-      <c r="O6" s="1">
-        <f t="shared" si="4"/>
-        <v>9720</v>
-      </c>
-      <c r="P6" s="1">
-        <f t="shared" si="5"/>
-        <v>63720</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="S6" s="10">
-        <f>MIN(P2:P7)</f>
         <v>53100</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>304</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>Ne</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Low</v>
-      </c>
-      <c r="I7" s="1">
-        <v>45000</v>
-      </c>
-      <c r="J7" s="1">
-        <f t="shared" si="7"/>
-        <v>45000</v>
-      </c>
-      <c r="K7" s="1">
-        <f t="shared" si="2"/>
-        <v>45000</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>January</v>
-      </c>
-      <c r="N7" s="4">
-        <f>VLOOKUP(F7,Product_Master!A1:C4,3,0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="O7" s="1">
-        <f t="shared" si="4"/>
-        <v>8100</v>
-      </c>
-      <c r="P7" s="1">
-        <f t="shared" si="5"/>
-        <v>53100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="14"/>
+      <c r="T8" s="6">
         <f>COUNTA(A2:A7)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q15" t="s">
+    <row r="9" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="13">
+        <f>SUMIF(B2:B7,"North",O2:O7)</f>
+        <v>177000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="13">
+        <f>SUMIF(B2:B7,"South",O2:O7)</f>
+        <v>194700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="13">
+        <f>SUMIF(B2:B7,"East",O2:O7)</f>
+        <v>63720</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="13">
+        <f>SUMIF(B2:B7,"West",O2:O7)</f>
+        <v>53100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:G15" xr:uid="{5BAACAB9-7624-49DE-9D30-6E31735D10DA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:P7">
-    <sortCondition descending="1" ref="P1:P7"/>
+  <autoFilter ref="E1:F15" xr:uid="{5BAACAB9-7624-49DE-9D30-6E31735D10DA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:O7">
+    <sortCondition descending="1" ref="O1:O7"/>
   </sortState>
-  <conditionalFormatting sqref="H2:H7">
+  <mergeCells count="1">
+    <mergeCell ref="R8:S8"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("High",G2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Low",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>60000</formula>
     </cfRule>
@@ -1334,7 +1396,7 @@
       <c r="G2" s="1">
         <v>92</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <f>AVERAGE(D2,E2,F2)</f>
         <v>81.666666666666671</v>
       </c>
@@ -1366,7 +1428,7 @@
       <c r="G3" s="1">
         <v>96</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <f t="shared" ref="H3:H6" si="1">AVERAGE(D3,E3,F3)</f>
         <v>89.666666666666671</v>
       </c>
@@ -1398,7 +1460,7 @@
       <c r="G4" s="1">
         <v>85</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -1406,11 +1468,11 @@
         <f t="shared" si="2"/>
         <v>Eligible</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="6">
+      <c r="N4" s="10"/>
+      <c r="O4" s="5">
         <f>MEDIAN(E2:E6)</f>
         <v>82</v>
       </c>
@@ -1438,7 +1500,7 @@
       <c r="G5" s="1">
         <v>98</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <f t="shared" si="1"/>
         <v>91.666666666666671</v>
       </c>
@@ -1470,7 +1532,7 @@
       <c r="G6" s="1">
         <v>80</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f t="shared" si="1"/>
         <v>57.666666666666664</v>
       </c>
